--- a/medical_surveys_questionnaires/006_cardiologists_event_log_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/006_cardiologists_event_log_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -823,8 +823,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -852,12 +852,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'highly_relevant',_'value':_'highly_relevant'}</t>
+          <t>highly_relevant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Highly Relevant', 'value': 'highly_relevant'}</t>
+          <t>Highly Relevant</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_relevant',_'value':_'somewhat_relevant'}</t>
+          <t>somewhat_relevant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Relevant', 'value': 'somewhat_relevant'}</t>
+          <t>Somewhat Relevant</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_relevant',_'value':_'not_relevant'}</t>
+          <t>not_very_relevant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not Very Relevant', 'value': 'not_relevant'}</t>
+          <t>Not Very Relevant</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'not_relevant_at_all',_'value':_'none'}</t>
+          <t>not_relevant_at_all</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Not Relevant At All', 'value': 'none'}</t>
+          <t>Not Relevant At All</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied',_'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied', 'value': 'very_satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied',_'value':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied', 'value': 'satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 'neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'dissatisfied',_'value':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Dissatisfied', 'value': 'dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_am_open_to_it',_'value':_true}</t>
+          <t>yes,_i_am_open_to_it</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I am open to it', 'value': True}</t>
+          <t>Yes, I am open to it</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'no,_please_do_not_contact_me',_'value':_false}</t>
+          <t>no,_please_do_not_contact_me</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'No, please do not contact me', 'value': False}</t>
+          <t>No, please do not contact me</t>
         </is>
       </c>
     </row>
